--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T09:14:32+00:00</t>
+    <t>2026-03-01T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t xml:space="preserve"> AT PreNUDGE Observation WHOQOL-BREF Score</t>
+    <t>AT PreNUDGE Observation WHOQOL-BREF Score</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1030,7 +1030,7 @@
 </t>
   </si>
   <si>
-    <t>Date/Time this version was made available</t>
+    <t>The mandatory date/time this version was made available</t>
   </si>
   <si>
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}whoqol-score-range:All WHOQOL-BREF component score values must be between 0 and 100. {component.value.ofType(Quantity).value.all($this &gt;= 0 and $this &lt;= 100)}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}at-prenudge-result-present:A PreNUDGE Observation must contain a root result, a root data absent reason, or at least one component result or component data absent reason. {value.exists() or dataAbsentReason.exists() or component.where(value.exists() or dataAbsentReason.exists()).exists()}whoqol-score-range:All WHOQOL-BREF component score values must be between 0 and 100. {component.value.ofType(Quantity).value.all($this &gt;= 0 and $this &lt;= 100)}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1114,7 +1114,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the result is missing</t>
+    <t>Reason why no clinically or analytically meaningful result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
@@ -1594,7 +1594,7 @@
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
-    <t>Why the component result is missing</t>
+    <t>Reason why no clinically or analytically meaningful component result is available</t>
   </si>
   <si>
     <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
@@ -6294,7 +6294,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>350</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -9304,7 +9304,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>502</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
@@ -11242,7 +11242,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>572</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -13180,7 +13180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>590</v>
       </c>
@@ -13199,7 +13199,7 @@
         <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>21</v>
@@ -15118,7 +15118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>608</v>
       </c>
@@ -15137,7 +15137,7 @@
         <v>93</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>21</v>
@@ -17056,7 +17056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>626</v>
       </c>
@@ -17075,7 +17075,7 @@
         <v>93</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>21</v>
@@ -18994,7 +18994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
         <v>644</v>
       </c>
@@ -19013,7 +19013,7 @@
         <v>93</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-whoqol-bref-score-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
